--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/Etrbondbiddingresult001Dto.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/Etrbondbiddingresult001Dto.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\ChongQingTouZi\tams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="13590" windowHeight="5985"/>
   </bookViews>
@@ -62,15 +67,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>投标券面总额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中标券面总额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>投标日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>投标券面总额/万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中标券面总额/万元</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -78,6 +83,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.0000_ "/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -123,7 +131,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -138,6 +146,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -411,7 +425,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -431,7 +445,9 @@
     <col min="8" max="8" width="13.125" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="12.5" customWidth="1"/>
-    <col min="11" max="14" width="12.5" style="3" customWidth="1"/>
+    <col min="11" max="11" width="16.125" style="6" customWidth="1"/>
+    <col min="12" max="12" width="16.25" style="6" customWidth="1"/>
+    <col min="13" max="14" width="12.5" style="3" customWidth="1"/>
     <col min="15" max="15" width="13.5" customWidth="1"/>
     <col min="16" max="16" width="12.875" customWidth="1"/>
     <col min="17" max="17" width="12.875" style="3" customWidth="1"/>
@@ -469,11 +485,11 @@
       <c r="J1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" s="4" t="s">
+      <c r="K1" s="5" t="s">
         <v>13</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="M1" s="4" t="s">
         <v>5</v>
@@ -482,11 +498,12 @@
         <v>6</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>